--- a/developer_week_01.xlsx
+++ b/developer_week_01.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\workspace\EnglishDeveloper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uuario\Documents\workspace\EnglishDeveloper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C07CB4-C115-4262-BEFA-B1722446B6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40121041-F00D-44F0-B91A-FA11F2AF7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="217">
   <si>
     <t>approach</t>
   </si>
@@ -559,6 +560,123 @@
   </si>
   <si>
     <t>performes</t>
+  </si>
+  <si>
+    <t>stepmon</t>
+  </si>
+  <si>
+    <t>madrasta</t>
+  </si>
+  <si>
+    <t>almost</t>
+  </si>
+  <si>
+    <t>casi</t>
+  </si>
+  <si>
+    <t>pussy</t>
+  </si>
+  <si>
+    <t>ask</t>
+  </si>
+  <si>
+    <t>preguntar</t>
+  </si>
+  <si>
+    <t>speding</t>
+  </si>
+  <si>
+    <t>decir</t>
+  </si>
+  <si>
+    <t>juice</t>
+  </si>
+  <si>
+    <t>jugo</t>
+  </si>
+  <si>
+    <t>drooling</t>
+  </si>
+  <si>
+    <t>babeo</t>
+  </si>
+  <si>
+    <t>narrow</t>
+  </si>
+  <si>
+    <t>estrecho</t>
+  </si>
+  <si>
+    <t>nerrou</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>amable, tipo</t>
+  </si>
+  <si>
+    <t>seem</t>
+  </si>
+  <si>
+    <t>parece</t>
+  </si>
+  <si>
+    <t>remain</t>
+  </si>
+  <si>
+    <t>permanecer</t>
+  </si>
+  <si>
+    <t>rimein</t>
+  </si>
+  <si>
+    <t>hopefully</t>
+  </si>
+  <si>
+    <t>espero</t>
+  </si>
+  <si>
+    <t>/'joup fely</t>
+  </si>
+  <si>
+    <t>snore</t>
+  </si>
+  <si>
+    <t>roncar</t>
+  </si>
+  <si>
+    <t>snour</t>
+  </si>
+  <si>
+    <t>saw</t>
+  </si>
+  <si>
+    <t>vi</t>
+  </si>
+  <si>
+    <t>took</t>
+  </si>
+  <si>
+    <t>quitar</t>
+  </si>
+  <si>
+    <t>ride</t>
+  </si>
+  <si>
+    <t>montar, cavalgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">take </t>
+  </si>
+  <si>
+    <t>tomar</t>
+  </si>
+  <si>
+    <t>cum</t>
+  </si>
+  <si>
+    <t>gozar</t>
   </si>
 </sst>
 </file>
@@ -1701,4 +1819,178 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB9EE66-E92C-45DE-9D78-2520F571E222}">
+  <dimension ref="A2:D20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/developer_week_01.xlsx
+++ b/developer_week_01.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uuario\Documents\workspace\EnglishDeveloper\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40121041-F00D-44F0-B91A-FA11F2AF7C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -26,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="237">
   <si>
     <t>approach</t>
   </si>
@@ -220,9 +214,6 @@
     <t>any</t>
   </si>
   <si>
-    <t xml:space="preserve"> cualquier</t>
-  </si>
-  <si>
     <t>keep</t>
   </si>
   <si>
@@ -607,9 +598,6 @@
     <t>estrecho</t>
   </si>
   <si>
-    <t>nerrou</t>
-  </si>
-  <si>
     <t>kind</t>
   </si>
   <si>
@@ -628,27 +616,18 @@
     <t>permanecer</t>
   </si>
   <si>
-    <t>rimein</t>
-  </si>
-  <si>
     <t>hopefully</t>
   </si>
   <si>
     <t>espero</t>
   </si>
   <si>
-    <t>/'joup fely</t>
-  </si>
-  <si>
     <t>snore</t>
   </si>
   <si>
     <t>roncar</t>
   </si>
   <si>
-    <t>snour</t>
-  </si>
-  <si>
     <t>saw</t>
   </si>
   <si>
@@ -658,9 +637,6 @@
     <t>took</t>
   </si>
   <si>
-    <t>quitar</t>
-  </si>
-  <si>
     <t>ride</t>
   </si>
   <si>
@@ -676,13 +652,91 @@
     <t>cum</t>
   </si>
   <si>
-    <t>gozar</t>
+    <t>/'step-mam/</t>
+  </si>
+  <si>
+    <t>/ól-moust/</t>
+  </si>
+  <si>
+    <t>/eask/</t>
+  </si>
+  <si>
+    <t>touch</t>
+  </si>
+  <si>
+    <t>tocar</t>
+  </si>
+  <si>
+    <t>/tach/</t>
+  </si>
+  <si>
+    <t>coger, tomar</t>
+  </si>
+  <si>
+    <t>venirse</t>
+  </si>
+  <si>
+    <t>come</t>
+  </si>
+  <si>
+    <t>venir</t>
+  </si>
+  <si>
+    <t>/'kam/</t>
+  </si>
+  <si>
+    <t>came</t>
+  </si>
+  <si>
+    <t>vino (pasado de come)</t>
+  </si>
+  <si>
+    <t>/'keim/</t>
+  </si>
+  <si>
+    <t>/'pu-si/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cualquier, ningun</t>
+  </si>
+  <si>
+    <t>You have a narrow pussy.</t>
+  </si>
+  <si>
+    <t>/'kaind/</t>
+  </si>
+  <si>
+    <t>/''nerou/</t>
+  </si>
+  <si>
+    <t>/'joup fely/</t>
+  </si>
+  <si>
+    <t>/'ri-mein/</t>
+  </si>
+  <si>
+    <t>/'snour/</t>
+  </si>
+  <si>
+    <t>Your account remains active</t>
+  </si>
+  <si>
+    <t>busy</t>
+  </si>
+  <si>
+    <t>cansado</t>
+  </si>
+  <si>
+    <t>/'bi-zi/</t>
+  </si>
+  <si>
+    <t>/raid/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1020,15 +1074,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1050,7 +1104,7 @@
         <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1058,13 +1112,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -1075,13 +1129,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J3" t="s">
         <v>2</v>
@@ -1092,13 +1146,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1112,13 +1166,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s">
         <v>6</v>
@@ -1129,13 +1183,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1152,13 +1206,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
@@ -1169,13 +1223,13 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
         <v>12</v>
@@ -1189,7 +1243,7 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
         <v>40</v>
@@ -1203,7 +1257,7 @@
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1212,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1220,16 +1274,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1237,13 +1291,13 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1260,19 +1314,19 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1280,13 +1334,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1295,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1303,13 +1357,13 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -1320,13 +1374,13 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1338,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1346,13 +1400,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1361,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1369,13 +1423,13 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s">
         <v>28</v>
@@ -1386,13 +1440,13 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
         <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>92</v>
       </c>
       <c r="J19" t="s">
         <v>30</v>
@@ -1403,13 +1457,13 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
         <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1423,16 +1477,16 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1440,13 +1494,13 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
         <v>96</v>
-      </c>
-      <c r="D22" t="s">
-        <v>97</v>
       </c>
       <c r="J22" t="s">
         <v>34</v>
@@ -1457,13 +1511,13 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
         <v>35</v>
@@ -1474,16 +1528,16 @@
         <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
         <v>99</v>
       </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1491,13 +1545,13 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1514,16 +1568,16 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1537,10 +1591,10 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1548,13 +1602,13 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
         <v>104</v>
       </c>
-      <c r="D28" t="s">
-        <v>105</v>
-      </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1562,13 +1616,13 @@
         <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" t="s">
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1585,16 +1639,16 @@
         <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C30" t="s">
         <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1602,13 +1656,13 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
         <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J31" t="s">
         <v>55</v>
@@ -1619,16 +1673,16 @@
         <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
         <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1636,13 +1690,13 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1651,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1659,19 +1713,19 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1679,10 +1733,10 @@
         <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J35" t="s">
         <v>63</v>
@@ -1690,27 +1744,27 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
         <v>65</v>
       </c>
-      <c r="C36" t="s">
-        <v>66</v>
-      </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" t="s">
         <v>67</v>
       </c>
-      <c r="C37" t="s">
-        <v>68</v>
-      </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -1719,21 +1773,21 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="s">
         <v>69</v>
       </c>
-      <c r="B38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" t="s">
-        <v>70</v>
-      </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1745,75 +1799,108 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
         <v>71</v>
       </c>
-      <c r="B39" t="s">
-        <v>156</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" t="s">
         <v>117</v>
       </c>
-      <c r="B40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>118</v>
       </c>
-      <c r="D40" t="s">
-        <v>119</v>
-      </c>
       <c r="J40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" t="s">
         <v>120</v>
       </c>
-      <c r="B41" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>121</v>
       </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
       <c r="J41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" t="s">
         <v>123</v>
       </c>
-      <c r="B42" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>124</v>
       </c>
-      <c r="D42" t="s">
-        <v>125</v>
-      </c>
       <c r="J42" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45" t="s">
+        <v>234</v>
+      </c>
+      <c r="D45" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -1822,172 +1909,211 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB9EE66-E92C-45DE-9D78-2520F571E222}">
-  <dimension ref="A2:D20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
         <v>178</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>180</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>183</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>185</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>187</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>189</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>191</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>192</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B11" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>194</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>196</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>198</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>199</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>201</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>202</v>
       </c>
-      <c r="D14" t="s">
+      <c r="B16" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>204</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>205</v>
       </c>
-      <c r="D15" t="s">
+      <c r="B18" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C18" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>207</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>209</v>
       </c>
-      <c r="B17" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>213</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C21" t="s">
         <v>215</v>
-      </c>
-      <c r="B20" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/developer_week_01.xlsx
+++ b/developer_week_01.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="238">
   <si>
     <t>approach</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>/raid/</t>
+  </si>
+  <si>
+    <t>/tok/</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1077,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2077,6 +2080,9 @@
       <c r="B17" t="s">
         <v>216</v>
       </c>
+      <c r="C17" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
